--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C7689D-ABCC-A34B-BD84-4D3B5BB3DE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BA09B0-C033-D84D-A75B-1939B35A9AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="4" r:id="rId1"/>
@@ -835,17 +835,17 @@
     <t>1. Payback $136 for the fixed line fees</t>
   </si>
   <si>
-    <t>1. Cancel the 2 packs of cigarette.
-2. Cancel hair cut.</t>
-  </si>
-  <si>
     <t>~ Revlon color stay 20/10 - $53.9</t>
   </si>
   <si>
     <t>~ Debit For Octopus Card ($100). 20/10
 ~ Help mom to paid the fixline fees $136 - 20/10
 ~ Gandi domain name programming.website renewal $312.73 - 26/10
-~ HSBC Global Transfer Charges $70 - 26/10</t>
+~ HSBC Global Transfer Charges $70 - 26/10
+~ Round Trip to Kowloon East Hospital 30/10 - $4</t>
+  </si>
+  <si>
+    <t>1. Cancel hair cut.</t>
   </si>
   <si>
     <t>~ Food
@@ -856,7 +856,9 @@
    ~ Ustore 23/10 - $97
    ~ Best Mart 360 23/10 - $25
    ~ OK Store 25/10 - $63
-   ~ OK Store 27/10 - $26</t>
+   ~ OK Store 27/10 - $26
+   ~ OK Store - $25 (Octopus paid-need to confirm)
+   ~ Best Mart 360 30/10 - $25</t>
   </si>
 </sst>
 </file>
@@ -3257,7 +3259,7 @@
         <v>169</v>
       </c>
       <c r="C3" s="9">
-        <v>700</v>
+        <v>41.51</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -3288,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="9">
-        <v>49.7</v>
+        <v>724.7</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -3350,7 +3352,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="9">
-        <v>66.510000000000005</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -3412,7 +3414,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="9">
-        <v>35.700000000000003</v>
+        <v>31.7</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -3444,7 +3446,7 @@
       </c>
       <c r="C9" s="9">
         <f>SUM(C3:C8)</f>
-        <v>860.91000000000008</v>
+        <v>806.91000000000008</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -8556,7 +8558,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>700</v>
+        <v>41.51</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -8588,7 +8590,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>49.7</v>
+        <v>724.7</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -8652,7 +8654,7 @@
       </c>
       <c r="C6" s="9">
         <f>'April 2026 - June 2026'!C6</f>
-        <v>66.510000000000005</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -8715,7 +8717,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>35.700000000000003</v>
+        <v>31.7</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -8747,7 +8749,7 @@
       </c>
       <c r="C9" s="9">
         <f>'April 2026 - June 2026'!C9</f>
-        <v>860.91000000000008</v>
+        <v>806.91000000000008</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -13696,7 +13698,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>700</v>
+        <v>41.51</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -13728,7 +13730,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>49.7</v>
+        <v>724.7</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -13792,7 +13794,7 @@
       </c>
       <c r="C6" s="9">
         <f>'April 2026 - June 2026'!C6</f>
-        <v>66.510000000000005</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -13855,7 +13857,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>35.700000000000003</v>
+        <v>31.7</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -13887,7 +13889,7 @@
       </c>
       <c r="C9" s="9">
         <f>'April 2026 - June 2026'!C9</f>
-        <v>860.91000000000008</v>
+        <v>806.91000000000008</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -13997,17 +13999,17 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
         <v>143</v>
       </c>
       <c r="B14" s="50"/>
       <c r="C14" s="102" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D14" s="103"/>
       <c r="E14" s="33">
-        <v>695</v>
+        <v>55</v>
       </c>
       <c r="H14" s="106"/>
       <c r="I14" s="106"/>
@@ -14072,7 +14074,7 @@
       </c>
       <c r="E18" s="26">
         <f>SUM(E13:E17)</f>
-        <v>3470.72</v>
+        <v>2830.72</v>
       </c>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
@@ -14649,7 +14651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="157" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" ht="178" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="82"/>
       <c r="B75" s="82"/>
       <c r="C75" s="83" t="s">
@@ -14657,25 +14659,25 @@
       </c>
       <c r="D75" s="84"/>
       <c r="E75" s="45">
-        <v>385.9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="86" customHeight="1" x14ac:dyDescent="0.2">
+        <v>435.9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="82"/>
       <c r="B76" s="82"/>
       <c r="C76" s="87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D76" s="88"/>
       <c r="E76" s="45">
-        <v>618.73</v>
+        <v>622.73</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="82"/>
       <c r="B77" s="82"/>
       <c r="C77" s="83" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D77" s="85"/>
       <c r="E77" s="45">
@@ -14701,7 +14703,7 @@
       <c r="D79" s="81"/>
       <c r="E79" s="47">
         <f>(E18+E73)-SUM(E74:E78)</f>
-        <v>860.91000000000122</v>
+        <v>166.91000000000076</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -14736,7 +14738,7 @@
       <c r="D83" s="62"/>
       <c r="E83" s="47">
         <f>E79</f>
-        <v>860.91000000000122</v>
+        <v>166.91000000000076</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -14807,7 +14809,7 @@
       <c r="D90" s="63"/>
       <c r="E90" s="47">
         <f>(E24+E83)-SUM(E84:E89)</f>
-        <v>1794.9100000000012</v>
+        <v>1100.9100000000008</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -14855,7 +14857,7 @@
       <c r="D95" s="62"/>
       <c r="E95" s="47">
         <f>E90</f>
-        <v>1794.9100000000012</v>
+        <v>1100.9100000000008</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -14908,7 +14910,7 @@
       <c r="D100" s="63"/>
       <c r="E100" s="47">
         <f>(E30+E95)-SUM(E96:E99)</f>
-        <v>2728.9100000000017</v>
+        <v>2034.9100000000008</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BA09B0-C033-D84D-A75B-1939B35A9AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA1806B-983B-E342-AF43-94664950B81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="188">
   <si>
     <t>Assets</t>
   </si>
@@ -859,6 +859,15 @@
    ~ OK Store 27/10 - $26
    ~ OK Store - $25 (Octopus paid-need to confirm)
    ~ Best Mart 360 30/10 - $25</t>
+  </si>
+  <si>
+    <t>01st November 2026</t>
+  </si>
+  <si>
+    <t>Cigarette</t>
+  </si>
+  <si>
+    <t>1. Cigarette charge for $300 per pack (buy 2 packs). $40 return</t>
   </si>
 </sst>
 </file>
@@ -13655,7 +13664,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A7D833F-4941-DA48-8974-C05250C51A36}">
-  <dimension ref="A1:Y1036"/>
+  <dimension ref="A1:Y1037"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -14048,7 +14057,7 @@
       <c r="H16" s="106"/>
       <c r="I16" s="106"/>
     </row>
-    <row r="17" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
         <v>143</v>
       </c>
@@ -14065,292 +14074,300 @@
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
     </row>
-    <row r="18" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="26">
-        <f>SUM(E13:E17)</f>
-        <v>2830.72</v>
+    <row r="18" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="101" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="93"/>
+      <c r="E18" s="29">
+        <v>40</v>
       </c>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
     </row>
     <row r="19" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="24"/>
       <c r="B19" s="24"/>
-      <c r="H19" s="60"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="26">
+        <f>SUM(E13:E18)</f>
+        <v>2870.72</v>
+      </c>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106"/>
     </row>
     <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="91" t="s">
+      <c r="B20" s="24"/>
+      <c r="H20" s="60"/>
+    </row>
+    <row r="21" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="91" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="91"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-    </row>
-    <row r="21" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="31" t="s">
+      <c r="B21" s="91"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+    </row>
+    <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B22" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C22" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="92"/>
-      <c r="E21" s="2" t="s">
+      <c r="D22" s="92"/>
+      <c r="E22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="50" t="s">
+    <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="93" t="s">
+      <c r="C23" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="93"/>
-      <c r="E22" s="29">
+      <c r="D23" s="93"/>
+      <c r="E23" s="29">
         <v>2485</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="54"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="108"/>
-      <c r="E23" s="29">
+    <row r="24" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="108"/>
+      <c r="E24" s="29">
         <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="26">
-        <f>SUM(E22:E23)</f>
-        <v>2485</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="24"/>
       <c r="B25" s="24"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="26">
+        <f>SUM(E23:E24)</f>
+        <v>2485</v>
+      </c>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+    </row>
+    <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="11"/>
-    </row>
-    <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="31" t="s">
+      <c r="B27" s="91"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
+    </row>
+    <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B28" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="92" t="s">
+      <c r="C28" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="92"/>
-      <c r="E27" s="2" t="s">
+      <c r="D28" s="92"/>
+      <c r="E28" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="50" t="s">
+    <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C29" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="93"/>
-      <c r="E28" s="33">
+      <c r="D29" s="93"/>
+      <c r="E29" s="33">
         <v>2485</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="29">
+    <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="29">
         <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="35">
-        <f>SUM(E28:E29)</f>
-        <v>2485</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="24"/>
       <c r="B31" s="24"/>
-    </row>
-    <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="94" t="s">
+      <c r="C31" s="5"/>
+      <c r="D31" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="35">
+        <f>SUM(E29:E30)</f>
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="94" t="s">
         <v>146</v>
       </c>
-      <c r="B32" s="94"/>
-      <c r="C32" s="94"/>
-    </row>
-    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="B33" s="94"/>
+      <c r="C33" s="94"/>
+    </row>
+    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C34" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="37"/>
-    </row>
-    <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="95" t="s">
+      <c r="D34" s="37"/>
+    </row>
+    <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="95"/>
-      <c r="C34" s="95"/>
-    </row>
-    <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="50" t="s">
+      <c r="B35" s="95"/>
+      <c r="C35" s="95"/>
+    </row>
+    <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="50" t="s">
+      <c r="B36" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C36" s="33">
         <v>78</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="38">
-        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B38" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="38">
+      <c r="C38" s="38">
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="7"/>
-      <c r="B38" s="6" t="s">
+    <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="7"/>
+      <c r="B39" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="39">
-        <f>SUM(C35:C37)</f>
+      <c r="C39" s="39">
+        <f>SUM(C36:C38)</f>
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="96" t="s">
+    <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="96"/>
-      <c r="C39" s="96"/>
-    </row>
-    <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="96"/>
       <c r="B40" s="96"/>
       <c r="C40" s="96"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="29">
-        <v>0</v>
-      </c>
+      <c r="A41" s="96"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
     </row>
     <row r="42" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" s="6"/>
-      <c r="C42" s="19">
+      <c r="C42" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="19">
@@ -14359,7 +14376,7 @@
     </row>
     <row r="44" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="19">
@@ -14367,156 +14384,154 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6" t="s">
+      <c r="A45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="39">
-        <f>SUM(C41:C44)</f>
+      <c r="C46" s="39">
+        <f>SUM(C42:C45)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="95" t="s">
+    <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="95"/>
-      <c r="C46" s="95"/>
-    </row>
-    <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" s="33">
-        <v>0</v>
-      </c>
+      <c r="B47" s="95"/>
+      <c r="C47" s="95"/>
     </row>
     <row r="48" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C48" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="6"/>
+      <c r="A49" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="B49" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="39">
-        <f>SUM(C47:C48)</f>
+      <c r="C50" s="39">
+        <f>SUM(C48:C49)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="95" t="s">
+    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="95"/>
-      <c r="C50" s="95"/>
-    </row>
-    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
+      <c r="B51" s="95"/>
+      <c r="C51" s="95"/>
+    </row>
+    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B52" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17" t="s">
+    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="39">
-        <f>SUM(C51)</f>
+      <c r="C53" s="39">
+        <f>SUM(C52)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="95" t="s">
+    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="95"/>
-      <c r="C53" s="95"/>
-    </row>
-    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
+      <c r="B54" s="95"/>
+      <c r="C54" s="95"/>
+    </row>
+    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B55" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6" t="s">
+    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C55" s="39">
-        <f>SUM(C54)</f>
+      <c r="C56" s="39">
+        <f>SUM(C55)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="89" t="s">
+    <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="89"/>
-      <c r="C56" s="89"/>
-    </row>
-    <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="17" t="s">
+      <c r="B57" s="89"/>
+      <c r="C57" s="89"/>
+    </row>
+    <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="40">
+      <c r="C58" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
+    <row r="59" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B58" s="50" t="s">
+      <c r="B59" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <v>1280</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
+    <row r="60" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B60" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="C59" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="C60" s="29">
         <v>0</v>
@@ -14524,53 +14539,55 @@
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="29">
+      <c r="B62" s="6"/>
+      <c r="C62" s="29">
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
+    <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="56" t="s">
+      <c r="B63" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="C62" s="19">
+      <c r="C63" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7" t="s">
+    <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C63" s="39">
-        <f>SUM(C57:C62)</f>
+      <c r="C64" s="39">
+        <f>SUM(C58:C63)</f>
         <v>1335</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="89" t="s">
+    <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="B64" s="89"/>
-      <c r="C64" s="89"/>
-    </row>
-    <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="19">
-        <v>0</v>
-      </c>
+      <c r="B65" s="89"/>
+      <c r="C65" s="89"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="19">
@@ -14578,246 +14595,248 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7" t="s">
+      <c r="A67" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67" s="7"/>
+      <c r="C67" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="19">
-        <f>SUM(C65:C66)</f>
+      <c r="C68" s="19">
+        <f>SUM(C66:C67)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="6"/>
-      <c r="B68" s="34" t="s">
+    <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="6"/>
+      <c r="B69" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="41">
-        <f>C38+C45+C49+C52+C55+C63</f>
+      <c r="C69" s="41">
+        <f>C39+C46+C50+C53+C56+C64</f>
         <v>1551</v>
       </c>
-      <c r="H68" s="42"/>
-    </row>
-    <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="24"/>
-      <c r="B69" s="24"/>
+      <c r="H69" s="42"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="24"/>
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="74" t="s">
+      <c r="A71" s="24"/>
+      <c r="B71" s="24"/>
+    </row>
+    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-    </row>
-    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="90" t="s">
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+    </row>
+    <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="90"/>
-      <c r="C72" s="90" t="s">
+      <c r="B73" s="90"/>
+      <c r="C73" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="D72" s="90"/>
-      <c r="E72" s="44" t="s">
+      <c r="D73" s="90"/>
+      <c r="E73" s="44" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="64" t="s">
+    <row r="74" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="64" t="s">
         <v>155</v>
       </c>
-      <c r="B73" s="64"/>
-      <c r="C73" s="61"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="47">
+      <c r="B74" s="64"/>
+      <c r="C74" s="61"/>
+      <c r="D74" s="61"/>
+      <c r="E74" s="47">
         <f>'July 2026- September 2026'!E102</f>
         <v>-0.27999999999883585</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="82" t="s">
+    <row r="75" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="B74" s="82"/>
-      <c r="C74" s="77"/>
-      <c r="D74" s="77"/>
-      <c r="E74" s="45">
+      <c r="B75" s="82"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="77"/>
+      <c r="E75" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="178" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="82"/>
-      <c r="B75" s="82"/>
-      <c r="C75" s="83" t="s">
-        <v>184</v>
-      </c>
-      <c r="D75" s="84"/>
-      <c r="E75" s="45">
-        <v>435.9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="103" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" ht="178" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="82"/>
       <c r="B76" s="82"/>
-      <c r="C76" s="87" t="s">
-        <v>182</v>
-      </c>
-      <c r="D76" s="88"/>
+      <c r="C76" s="83" t="s">
+        <v>184</v>
+      </c>
+      <c r="D76" s="84"/>
       <c r="E76" s="45">
-        <v>622.73</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+        <v>435.9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="82"/>
       <c r="B77" s="82"/>
-      <c r="C77" s="83" t="s">
+      <c r="C77" s="87" t="s">
+        <v>182</v>
+      </c>
+      <c r="D77" s="88"/>
+      <c r="E77" s="45">
+        <v>622.73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="82"/>
+      <c r="B78" s="82"/>
+      <c r="C78" s="83" t="s">
         <v>181</v>
       </c>
-      <c r="D77" s="85"/>
-      <c r="E77" s="45">
+      <c r="D78" s="85"/>
+      <c r="E78" s="45">
         <v>53.9</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="82" t="s">
+    <row r="79" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="B78" s="82"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="86"/>
-      <c r="E78" s="46">
-        <f>C68</f>
+      <c r="B79" s="82"/>
+      <c r="C79" s="86"/>
+      <c r="D79" s="86"/>
+      <c r="E79" s="46">
+        <f>C69</f>
         <v>1551</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C79" s="81" t="s">
+    <row r="80" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C80" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D79" s="81"/>
-      <c r="E79" s="47">
-        <f>(E18+E73)-SUM(E74:E78)</f>
-        <v>166.91000000000076</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="74" t="s">
-        <v>151</v>
-      </c>
-      <c r="B81" s="74"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
-    </row>
+      <c r="D80" s="81"/>
+      <c r="E80" s="47">
+        <f>(E19+E74)-SUM(E75:E79)</f>
+        <v>206.91000000000076</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="82" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="74" t="s">
+        <v>151</v>
+      </c>
+      <c r="B82" s="74"/>
+      <c r="C82" s="74"/>
+      <c r="D82" s="74"/>
+      <c r="E82" s="74"/>
+    </row>
+    <row r="83" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="74"/>
-      <c r="C82" s="74" t="s">
+      <c r="B83" s="74"/>
+      <c r="C83" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D82" s="74"/>
-      <c r="E82" s="43" t="s">
+      <c r="D83" s="74"/>
+      <c r="E83" s="43" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="64" t="s">
+    <row r="84" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="B83" s="64"/>
-      <c r="C83" s="62"/>
-      <c r="D83" s="62"/>
-      <c r="E83" s="47">
-        <f>E79</f>
-        <v>166.91000000000076</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="65" t="s">
+      <c r="B84" s="64"/>
+      <c r="C84" s="62"/>
+      <c r="D84" s="62"/>
+      <c r="E84" s="47">
+        <f>E80</f>
+        <v>206.91000000000076</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="B84" s="66"/>
-      <c r="C84" s="75"/>
-      <c r="D84" s="76"/>
-      <c r="E84" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="67"/>
-      <c r="B85" s="68"/>
-      <c r="C85" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="D85" s="77"/>
+      <c r="B85" s="66"/>
+      <c r="C85" s="75"/>
+      <c r="D85" s="76"/>
       <c r="E85" s="48">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="67"/>
       <c r="B86" s="68"/>
-      <c r="C86" s="78"/>
-      <c r="D86" s="79"/>
+      <c r="C86" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="D86" s="77"/>
       <c r="E86" s="48">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="67"/>
       <c r="B87" s="68"/>
-      <c r="C87" s="75"/>
-      <c r="D87" s="80"/>
+      <c r="C87" s="78"/>
+      <c r="D87" s="79"/>
       <c r="E87" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="69"/>
-      <c r="B88" s="70"/>
-      <c r="C88" s="78"/>
-      <c r="D88" s="79"/>
-      <c r="E88" s="55">
+      <c r="A88" s="67"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="75"/>
+      <c r="D88" s="80"/>
+      <c r="E88" s="48">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="61" t="s">
+    <row r="89" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="69"/>
+      <c r="B89" s="70"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="79"/>
+      <c r="E89" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="B89" s="61"/>
-      <c r="C89" s="62"/>
-      <c r="D89" s="62"/>
-      <c r="E89" s="45">
-        <f>C68</f>
+      <c r="B90" s="61"/>
+      <c r="C90" s="62"/>
+      <c r="D90" s="62"/>
+      <c r="E90" s="45">
+        <f>C69</f>
         <v>1551</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C90" s="63" t="s">
+    <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C91" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="63"/>
-      <c r="E90" s="47">
-        <f>(E24+E83)-SUM(E84:E89)</f>
-        <v>1100.9100000000008</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="49"/>
-      <c r="B91" s="49"/>
-      <c r="C91" s="49"/>
-      <c r="D91" s="49"/>
-      <c r="E91" s="49"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="47">
+        <f>(E25+E84)-SUM(E85:E90)</f>
+        <v>1140.9100000000008</v>
+      </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="49"/>
@@ -14826,96 +14845,99 @@
       <c r="D92" s="49"/>
       <c r="E92" s="49"/>
     </row>
-    <row r="93" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="73" t="s">
+    <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="49"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="49"/>
+      <c r="D93" s="49"/>
+      <c r="E93" s="49"/>
+    </row>
+    <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="73" t="s">
         <v>154</v>
       </c>
-      <c r="B93" s="73"/>
-      <c r="C93" s="73"/>
-      <c r="D93" s="73"/>
-      <c r="E93" s="73"/>
-    </row>
-    <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="74" t="s">
+      <c r="B94" s="73"/>
+      <c r="C94" s="73"/>
+      <c r="D94" s="73"/>
+      <c r="E94" s="73"/>
+    </row>
+    <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="B94" s="74"/>
-      <c r="C94" s="74" t="s">
+      <c r="B95" s="74"/>
+      <c r="C95" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="74"/>
-      <c r="E94" s="43" t="s">
+      <c r="D95" s="74"/>
+      <c r="E95" s="43" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="64" t="s">
+    <row r="96" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="64" t="s">
         <v>152</v>
       </c>
-      <c r="B95" s="64"/>
-      <c r="C95" s="62"/>
-      <c r="D95" s="62"/>
-      <c r="E95" s="47">
-        <f>E90</f>
-        <v>1100.9100000000008</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="65" t="s">
+      <c r="B96" s="64"/>
+      <c r="C96" s="62"/>
+      <c r="D96" s="62"/>
+      <c r="E96" s="47">
+        <f>E91</f>
+        <v>1140.9100000000008</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="B96" s="66"/>
-      <c r="C96" s="71"/>
-      <c r="D96" s="72"/>
-      <c r="E96" s="45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="67"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="71" t="s">
-        <v>157</v>
-      </c>
+      <c r="B97" s="66"/>
+      <c r="C97" s="71"/>
       <c r="D97" s="72"/>
       <c r="E97" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="69"/>
-      <c r="B98" s="70"/>
-      <c r="C98" s="71"/>
+    <row r="98" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="67"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="71" t="s">
+        <v>157</v>
+      </c>
       <c r="D98" s="72"/>
       <c r="E98" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="61" t="s">
+    <row r="99" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="69"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="B99" s="61"/>
-      <c r="C99" s="62"/>
-      <c r="D99" s="62"/>
-      <c r="E99" s="45">
-        <f>C68</f>
+      <c r="B100" s="61"/>
+      <c r="C100" s="62"/>
+      <c r="D100" s="62"/>
+      <c r="E100" s="45">
+        <f>C69</f>
         <v>1551</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C100" s="63" t="s">
+    <row r="101" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C101" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="D100" s="63"/>
-      <c r="E100" s="47">
-        <f>(E30+E95)-SUM(E96:E99)</f>
-        <v>2034.9100000000008</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="24"/>
-      <c r="B101" s="24"/>
+      <c r="D101" s="63"/>
+      <c r="E101" s="47">
+        <f>(E31+E96)-SUM(E97:E100)</f>
+        <v>2074.9100000000008</v>
+      </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="24"/>
@@ -18657,74 +18679,79 @@
       <c r="A1036" s="24"/>
       <c r="B1036" s="24"/>
     </row>
+    <row r="1037" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1037" s="24"/>
+      <c r="B1037" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="H14:I18"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="C21:D21"/>
+  <mergeCells count="65">
+    <mergeCell ref="H14:I19"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A40:C41"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B77"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A75:B78"/>
     <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
     <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A82:E82"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="C83:D83"/>
-    <mergeCell ref="A84:B88"/>
+    <mergeCell ref="A84:B84"/>
     <mergeCell ref="C84:D84"/>
+    <mergeCell ref="A85:B89"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="C88:D88"/>
-    <mergeCell ref="A89:B89"/>
     <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A90:B90"/>
     <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A95:B95"/>
     <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A96:B98"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A96:B96"/>
     <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B99"/>
     <mergeCell ref="C97:D97"/>
     <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
   </mergeCells>
-  <conditionalFormatting sqref="C8:C9 E73">
+  <conditionalFormatting sqref="C8:C9 E74">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -18732,7 +18759,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E79 E83 E90 E95 E100">
+  <conditionalFormatting sqref="E80 E84 E91 E96 E101">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
